--- a/EKG_Kalite_Yönetim_Sistemi/00_Yönetim Sistemi Çerçevesi/05_Ürün Güvenliği, Mevzuat ve Sorumluluk/EKG-YNT-LST-08_ecovadis_degerlendirmesi_ve_sorumlu_satinalma_taahhudu.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/00_Yönetim Sistemi Çerçevesi/05_Ürün Güvenliği, Mevzuat ve Sorumluluk/EKG-YNT-LST-08_ecovadis_degerlendirmesi_ve_sorumlu_satinalma_taahhudu.xlsx
@@ -844,7 +844,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-YNT-LST-08&amp;C&amp;"Arial,Regular"&amp;11EcoVadis Değerlendirmesi ve Sorumlu Satınalma Taahhüdü Kayıt Listesi</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 08.06.2026 | Revizyon: 15.09.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb3c8ea681b343f0"/>
   <x:tableParts count="1">
@@ -1126,7 +1127,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-YNT-LST-08&amp;C&amp;"Arial,Regular"&amp;11EcoVadis Değerlendirmesi ve Sorumlu Satınalma Taahhüdü Kayıt Listesi</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 08.06.2026 | Revizyon: 15.09.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86b99f9c2ff34ace"/>
   <x:tableParts count="1">
@@ -1426,7 +1428,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-YNT-LST-08&amp;C&amp;"Arial,Regular"&amp;11EcoVadis Değerlendirmesi ve Sorumlu Satınalma Taahhüdü Kayıt Listesi</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 08.06.2026 | Revizyon: 15.09.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R596eb1289d3a4ed2"/>
   <x:tableParts count="1">
